--- a/Configs/GameConfig/Datas/boss.xlsx
+++ b/Configs/GameConfig/Datas/boss.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9a00d88900d4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R683d0c495ee3468e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -366,53 +366,47 @@
         <x:v>name</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>originalSymbol</x:v>
+        <x:v>skillId</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>sourceRange</x:v>
+        <x:v>animationKey</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>skillId</x:v>
+        <x:v>resourcePath</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>animationKey</x:v>
+        <x:v>attackAnimation</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>resourcePath</x:v>
+        <x:v>idleAnimation</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>attackAnimation</x:v>
+        <x:v>timeline</x:v>
       </x:c>
       <x:c r="K1" t="str">
-        <x:v>followupAnimation</x:v>
+        <x:v>enabled</x:v>
       </x:c>
       <x:c r="L1" t="str">
-        <x:v>idleAnimation</x:v>
+        <x:v>healthMultiplier</x:v>
       </x:c>
       <x:c r="M1" t="str">
-        <x:v>timeline</x:v>
+        <x:v>moveSpeed</x:v>
       </x:c>
       <x:c r="N1" t="str">
-        <x:v>enabled</x:v>
+        <x:v>contactDamage</x:v>
       </x:c>
       <x:c r="O1" t="str">
-        <x:v>healthMultiplier</x:v>
+        <x:v>rewardGold</x:v>
       </x:c>
       <x:c r="P1" t="str">
-        <x:v>moveSpeed</x:v>
+        <x:v>logicalWidth</x:v>
       </x:c>
       <x:c r="Q1" t="str">
-        <x:v>contactDamage</x:v>
-      </x:c>
-      <x:c r="R1" t="str">
-        <x:v>rewardGold</x:v>
-      </x:c>
-      <x:c r="S1" t="str">
-        <x:v>logicalWidth</x:v>
-      </x:c>
-      <x:c r="T1" t="str">
         <x:v>logicalHeight</x:v>
       </x:c>
+      <x:c r="R1"/>
+      <x:c r="S1"/>
+      <x:c r="T1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -428,53 +422,47 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="F2" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>int</x:v>
+        <x:v>string?</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>string?</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>string</x:v>
+        <x:v>boss.Timeline</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>string?</x:v>
+        <x:v>bool</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>string</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>boss.Timeline</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>bool</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>float</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="P2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="R2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="S2" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="T2" t="str">
-        <x:v>float</x:v>
-      </x:c>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -505,62 +493,56 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
+        <x:v>主键，Boss 唯一 ID</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>资源名(原主键)</x:v>
+        <x:v>资源名，原主键，保留作溯源</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>名称</x:v>
+        <x:v>显示名</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>原始符号</x:v>
+        <x:v>技能 ID，引用 skill.Id，技能类别应为 boss</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>源码区间</x:v>
+        <x:v>Spine 表现绑定键，必填，如 boss0</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>技能ID</x:v>
+        <x:v>YooAsset Prefab 地址，非磁盘路径，如 ZhangLiang</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>动画键</x:v>
+        <x:v>Spine 普通攻击动画名，如 attackliang</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>资源路径</x:v>
+        <x:v>Spine 待机/移动循环动画名，如 goliang</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>攻击动画</x:v>
+        <x:v>技能时间轴：effectAtMs（效果提交时刻）/ completeAtMs（完成时刻），后者必须大于前者</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>后续动画</x:v>
+        <x:v>是否启用，只有启用 Boss 才允许进入正式计划</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>待机动画</x:v>
+        <x:v>Boss 基础生命倍率</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>时间轴</x:v>
+        <x:v>移动速度</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>是否启用</x:v>
+        <x:v>到达终点造成的伤害</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>生命倍率</x:v>
+        <x:v>击杀金币</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>移动速度</x:v>
+        <x:v>逻辑宽度，用于中心、范围及表现定位</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>终点接触伤害</x:v>
-      </x:c>
-      <x:c r="R4" t="str">
-        <x:v>击杀金币</x:v>
-      </x:c>
-      <x:c r="S4" t="str">
-        <x:v>逻辑宽度</x:v>
-      </x:c>
-      <x:c r="T4" t="str">
         <x:v>逻辑高度</x:v>
       </x:c>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -573,52 +555,48 @@
       <x:c r="D5" t="str">
         <x:v>张梁</x:v>
       </x:c>
-      <x:c r="E5" t="str">
-        <x:v>nj</x:v>
+      <x:c r="E5" t="n">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>32468-32631</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>8</x:v>
+        <x:v>boss0</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>ZhangLiang</x:v>
       </x:c>
       <x:c r="H5" t="str">
-        <x:v>boss0</x:v>
+        <x:v>attackliang</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>ZhangLiang</x:v>
+        <x:v>goliang</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>attackliang</x:v>
-      </x:c>
-      <x:c r="K5"/>
-      <x:c r="L5" t="str">
-        <x:v>goliang</x:v>
-      </x:c>
-      <x:c r="M5" t="str">
         <x:v>500,1400</x:v>
       </x:c>
-      <x:c r="N5" s="2" t="b">
+      <x:c r="K5" s="2" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="O5" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P5" t="n">
-        <x:v>10</x:v>
+        <x:v>84.33</x:v>
       </x:c>
       <x:c r="Q5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R5" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S5" t="n">
-        <x:v>84.33</x:v>
-      </x:c>
-      <x:c r="T5" t="n">
         <x:v>101.25</x:v>
       </x:c>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
@@ -631,50 +609,46 @@
       <x:c r="D6" t="str">
         <x:v>张宝</x:v>
       </x:c>
-      <x:c r="E6" t="str">
-        <x:v>oO</x:v>
+      <x:c r="E6" t="n">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>32632-32697</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>9</x:v>
-      </x:c>
+        <x:v>boss0</x:v>
+      </x:c>
+      <x:c r="G6"/>
       <x:c r="H6" t="str">
-        <x:v>boss0</x:v>
-      </x:c>
-      <x:c r="I6"/>
+        <x:v>attackbao</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>gobao</x:v>
+      </x:c>
       <x:c r="J6" t="str">
-        <x:v>attackbao</x:v>
-      </x:c>
-      <x:c r="K6"/>
-      <x:c r="L6" t="str">
-        <x:v>gobao</x:v>
-      </x:c>
-      <x:c r="M6" t="str">
         <x:v>0,1000</x:v>
       </x:c>
-      <x:c r="N6" s="2" t="b">
+      <x:c r="K6" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O6" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P6" t="n">
-        <x:v>10</x:v>
+        <x:v>84.33</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S6" t="n">
-        <x:v>84.33</x:v>
-      </x:c>
-      <x:c r="T6" t="n">
         <x:v>101.25</x:v>
       </x:c>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -687,50 +661,46 @@
       <x:c r="D7" t="str">
         <x:v>张角</x:v>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>tj</x:v>
+      <x:c r="E7" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>31120-31187</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>boss0</x:v>
+      </x:c>
+      <x:c r="G7"/>
       <x:c r="H7" t="str">
-        <x:v>boss0</x:v>
-      </x:c>
-      <x:c r="I7"/>
+        <x:v>attackjiao</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>gojiao</x:v>
+      </x:c>
       <x:c r="J7" t="str">
-        <x:v>attackjiao</x:v>
-      </x:c>
-      <x:c r="K7"/>
-      <x:c r="L7" t="str">
-        <x:v>gojiao</x:v>
-      </x:c>
-      <x:c r="M7" t="str">
         <x:v>500,1000</x:v>
       </x:c>
-      <x:c r="N7" s="2" t="b">
+      <x:c r="K7" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O7" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P7" t="n">
-        <x:v>10</x:v>
+        <x:v>84.33</x:v>
       </x:c>
       <x:c r="Q7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S7" t="n">
-        <x:v>84.33</x:v>
-      </x:c>
-      <x:c r="T7" t="n">
         <x:v>101.25</x:v>
       </x:c>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
+      <x:c r="T7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -743,50 +713,46 @@
       <x:c r="D8" t="str">
         <x:v>孙尚香</x:v>
       </x:c>
-      <x:c r="E8" t="str">
-        <x:v>oP</x:v>
+      <x:c r="E8" t="n">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>32875-32938</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>11</x:v>
-      </x:c>
+        <x:v>boss1</x:v>
+      </x:c>
+      <x:c r="G8"/>
       <x:c r="H8" t="str">
-        <x:v>boss1</x:v>
-      </x:c>
-      <x:c r="I8"/>
+        <x:v>attackxiang</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>goxiang</x:v>
+      </x:c>
       <x:c r="J8" t="str">
-        <x:v>attackxiang</x:v>
-      </x:c>
-      <x:c r="K8"/>
-      <x:c r="L8" t="str">
-        <x:v>goxiang</x:v>
-      </x:c>
-      <x:c r="M8" t="str">
         <x:v>500,1000</x:v>
       </x:c>
-      <x:c r="N8" s="2" t="b">
+      <x:c r="K8" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O8" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P8" t="n">
-        <x:v>10</x:v>
+        <x:v>79.69</x:v>
       </x:c>
       <x:c r="Q8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S8" t="n">
-        <x:v>79.69</x:v>
-      </x:c>
-      <x:c r="T8" t="n">
         <x:v>96.08</x:v>
       </x:c>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
+      <x:c r="T8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -799,50 +765,46 @@
       <x:c r="D9" t="str">
         <x:v>甄宓</x:v>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>rT</x:v>
+      <x:c r="E9" t="n">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>31188-31251</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>12</x:v>
-      </x:c>
+        <x:v>boss1</x:v>
+      </x:c>
+      <x:c r="G9"/>
       <x:c r="H9" t="str">
-        <x:v>boss1</x:v>
-      </x:c>
-      <x:c r="I9"/>
+        <x:v>attackzhen</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>gozhen</x:v>
+      </x:c>
       <x:c r="J9" t="str">
-        <x:v>attackzhen</x:v>
-      </x:c>
-      <x:c r="K9"/>
-      <x:c r="L9" t="str">
-        <x:v>gozhen</x:v>
-      </x:c>
-      <x:c r="M9" t="str">
         <x:v>900,1000</x:v>
       </x:c>
-      <x:c r="N9" s="2" t="b">
+      <x:c r="K9" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P9" t="n">
-        <x:v>10</x:v>
+        <x:v>79.69</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S9" t="n">
-        <x:v>79.69</x:v>
-      </x:c>
-      <x:c r="T9" t="n">
         <x:v>96.08</x:v>
       </x:c>
+      <x:c r="R9"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
@@ -855,50 +817,46 @@
       <x:c r="D10" t="str">
         <x:v>貂蝉</x:v>
       </x:c>
-      <x:c r="E10" t="str">
-        <x:v>sR</x:v>
+      <x:c r="E10" t="n">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F10" t="str">
-        <x:v>32264-32389</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>13</x:v>
-      </x:c>
+        <x:v>boss1</x:v>
+      </x:c>
+      <x:c r="G10"/>
       <x:c r="H10" t="str">
-        <x:v>boss1</x:v>
-      </x:c>
-      <x:c r="I10"/>
+        <x:v>attackdiao</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>godiao</x:v>
+      </x:c>
       <x:c r="J10" t="str">
-        <x:v>attackdiao</x:v>
-      </x:c>
-      <x:c r="K10"/>
-      <x:c r="L10" t="str">
-        <x:v>godiao</x:v>
-      </x:c>
-      <x:c r="M10" t="str">
         <x:v>200,1200</x:v>
       </x:c>
-      <x:c r="N10" s="2" t="b">
+      <x:c r="K10" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N10" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O10" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P10" t="n">
-        <x:v>10</x:v>
+        <x:v>79.69</x:v>
       </x:c>
       <x:c r="Q10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R10" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S10" t="n">
-        <x:v>79.69</x:v>
-      </x:c>
-      <x:c r="T10" t="n">
         <x:v>96.08</x:v>
       </x:c>
+      <x:c r="R10"/>
+      <x:c r="S10"/>
+      <x:c r="T10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -911,50 +869,46 @@
       <x:c r="D11" t="str">
         <x:v>华雄</x:v>
       </x:c>
-      <x:c r="E11" t="str">
-        <x:v>tz</x:v>
+      <x:c r="E11" t="n">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F11" t="str">
-        <x:v>32753-32804</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>14</x:v>
-      </x:c>
+        <x:v>huaXiong</x:v>
+      </x:c>
+      <x:c r="G11"/>
       <x:c r="H11" t="str">
-        <x:v>huaXiong</x:v>
-      </x:c>
-      <x:c r="I11"/>
+        <x:v>attackhx</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>gohx</x:v>
+      </x:c>
       <x:c r="J11" t="str">
-        <x:v>attackhx</x:v>
-      </x:c>
-      <x:c r="K11"/>
-      <x:c r="L11" t="str">
-        <x:v>gohx</x:v>
-      </x:c>
-      <x:c r="M11" t="str">
         <x:v>500,1000</x:v>
       </x:c>
-      <x:c r="N11" s="2" t="b">
+      <x:c r="K11" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P11" t="n">
-        <x:v>10</x:v>
+        <x:v>90.92</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S11" t="n">
-        <x:v>90.92</x:v>
-      </x:c>
-      <x:c r="T11" t="n">
         <x:v>164.08</x:v>
       </x:c>
+      <x:c r="R11"/>
+      <x:c r="S11"/>
+      <x:c r="T11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
@@ -967,50 +921,46 @@
       <x:c r="D12" t="str">
         <x:v>吕布</x:v>
       </x:c>
-      <x:c r="E12" t="str">
-        <x:v>nJ</x:v>
+      <x:c r="E12" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F12" t="str">
-        <x:v>31649-31712</x:v>
-      </x:c>
-      <x:c r="G12" t="n">
-        <x:v>15</x:v>
-      </x:c>
+        <x:v>lvBu</x:v>
+      </x:c>
+      <x:c r="G12"/>
       <x:c r="H12" t="str">
-        <x:v>lvBu</x:v>
-      </x:c>
-      <x:c r="I12"/>
+        <x:v>attacklvbu</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>golvbu</x:v>
+      </x:c>
       <x:c r="J12" t="str">
-        <x:v>attacklvbu</x:v>
-      </x:c>
-      <x:c r="K12"/>
-      <x:c r="L12" t="str">
-        <x:v>golvbu</x:v>
-      </x:c>
-      <x:c r="M12" t="str">
         <x:v>650,1000</x:v>
       </x:c>
-      <x:c r="N12" s="2" t="b">
+      <x:c r="K12" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N12" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O12" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P12" t="n">
-        <x:v>10</x:v>
+        <x:v>302.23</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R12" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S12" t="n">
         <x:v>302.23</x:v>
       </x:c>
-      <x:c r="T12" t="n">
-        <x:v>302.23</x:v>
-      </x:c>
+      <x:c r="R12"/>
+      <x:c r="S12"/>
+      <x:c r="T12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
@@ -1023,52 +973,46 @@
       <x:c r="D13" t="str">
         <x:v>董卓</x:v>
       </x:c>
-      <x:c r="E13" t="str">
-        <x:v>oA</x:v>
+      <x:c r="E13" t="n">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F13" t="str">
-        <x:v>32144-32257</x:v>
-      </x:c>
-      <x:c r="G13" t="n">
-        <x:v>16</x:v>
-      </x:c>
+        <x:v>dongZhuo</x:v>
+      </x:c>
+      <x:c r="G13"/>
       <x:c r="H13" t="str">
-        <x:v>dongZhuo</x:v>
-      </x:c>
-      <x:c r="I13"/>
+        <x:v>attackdz</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>godz</x:v>
+      </x:c>
       <x:c r="J13" t="str">
-        <x:v>attackdz</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>attack2dz</x:v>
-      </x:c>
-      <x:c r="L13" t="str">
-        <x:v>godz</x:v>
-      </x:c>
-      <x:c r="M13" t="str">
         <x:v>500,1400</x:v>
       </x:c>
-      <x:c r="N13" s="2" t="b">
+      <x:c r="K13" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N13" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O13" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P13" t="n">
-        <x:v>10</x:v>
+        <x:v>285.5</x:v>
       </x:c>
       <x:c r="Q13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R13" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S13" t="n">
-        <x:v>285.5</x:v>
-      </x:c>
-      <x:c r="T13" t="n">
         <x:v>256</x:v>
       </x:c>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
+      <x:c r="T13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
@@ -1081,50 +1025,46 @@
       <x:c r="D14" t="str">
         <x:v>典韦</x:v>
       </x:c>
-      <x:c r="E14" t="str">
-        <x:v>rv</x:v>
+      <x:c r="E14" t="n">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>31485-31648</x:v>
-      </x:c>
-      <x:c r="G14" t="n">
-        <x:v>17</x:v>
-      </x:c>
+        <x:v>boss2</x:v>
+      </x:c>
+      <x:c r="G14"/>
       <x:c r="H14" t="str">
-        <x:v>boss2</x:v>
-      </x:c>
-      <x:c r="I14"/>
+        <x:v>attackdian</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>godian</x:v>
+      </x:c>
       <x:c r="J14" t="str">
-        <x:v>attackdian</x:v>
-      </x:c>
-      <x:c r="K14"/>
-      <x:c r="L14" t="str">
-        <x:v>godian</x:v>
-      </x:c>
-      <x:c r="M14" t="str">
         <x:v>800,1400</x:v>
       </x:c>
-      <x:c r="N14" s="2" t="b">
+      <x:c r="K14" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N14" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O14" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P14" t="n">
-        <x:v>10</x:v>
+        <x:v>58.1</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S14" t="n">
-        <x:v>58.1</x:v>
-      </x:c>
-      <x:c r="T14" t="n">
         <x:v>83.39</x:v>
       </x:c>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
+      <x:c r="T14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
@@ -1137,50 +1077,46 @@
       <x:c r="D15" t="str">
         <x:v>夏侯惇</x:v>
       </x:c>
-      <x:c r="E15" t="str">
-        <x:v>q5</x:v>
+      <x:c r="E15" t="n">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>31713-31783</x:v>
-      </x:c>
-      <x:c r="G15" t="n">
-        <x:v>18</x:v>
-      </x:c>
+        <x:v>boss2</x:v>
+      </x:c>
+      <x:c r="G15"/>
       <x:c r="H15" t="str">
-        <x:v>boss2</x:v>
-      </x:c>
-      <x:c r="I15"/>
+        <x:v>attackdun</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>goxia</x:v>
+      </x:c>
       <x:c r="J15" t="str">
-        <x:v>attackdun</x:v>
-      </x:c>
-      <x:c r="K15"/>
-      <x:c r="L15" t="str">
-        <x:v>goxia</x:v>
-      </x:c>
-      <x:c r="M15" t="str">
         <x:v>1000,1500</x:v>
       </x:c>
-      <x:c r="N15" s="2" t="b">
+      <x:c r="K15" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N15" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O15" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P15" t="n">
-        <x:v>10</x:v>
+        <x:v>58.1</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S15" t="n">
-        <x:v>58.1</x:v>
-      </x:c>
-      <x:c r="T15" t="n">
         <x:v>83.39</x:v>
       </x:c>
+      <x:c r="R15"/>
+      <x:c r="S15"/>
+      <x:c r="T15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -1193,50 +1129,46 @@
       <x:c r="D16" t="str">
         <x:v>曹操</x:v>
       </x:c>
-      <x:c r="E16" t="str">
-        <x:v>vg</x:v>
+      <x:c r="E16" t="n">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>31001-31119</x:v>
-      </x:c>
-      <x:c r="G16" t="n">
-        <x:v>19</x:v>
-      </x:c>
+        <x:v>boss2</x:v>
+      </x:c>
+      <x:c r="G16"/>
       <x:c r="H16" t="str">
-        <x:v>boss2</x:v>
-      </x:c>
-      <x:c r="I16"/>
+        <x:v>attackcao</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>gocao</x:v>
+      </x:c>
       <x:c r="J16" t="str">
-        <x:v>attackcao</x:v>
-      </x:c>
-      <x:c r="K16"/>
-      <x:c r="L16" t="str">
-        <x:v>gocao</x:v>
-      </x:c>
-      <x:c r="M16" t="str">
         <x:v>900,1000</x:v>
       </x:c>
-      <x:c r="N16" s="2" t="b">
+      <x:c r="K16" s="2" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N16" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O16" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P16" t="n">
-        <x:v>10</x:v>
+        <x:v>58.1</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S16" t="n">
-        <x:v>58.1</x:v>
-      </x:c>
-      <x:c r="T16" t="n">
         <x:v>83.39</x:v>
       </x:c>
+      <x:c r="R16"/>
+      <x:c r="S16"/>
+      <x:c r="T16"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
